--- a/consent_forms/032_personal_injury_doctors_agreement--consent_forms.xlsx
+++ b/consent_forms/032_personal_injury_doctors_agreement--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'option_1',_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Option 1', 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'option_2',_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Option 2', 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'option_3',_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Option 3', 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'option_4',_'label':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Option 4', 'label': 'Option 4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'option_a',_'label':_'option_a'}</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Option A', 'label': 'Option A'}</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'option_b',_'label':_'option_b'}</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Option B', 'label': 'Option B'}</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'option_c',_'label':_'option_c'}</t>
+          <t>option_c</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Option C', 'label': 'Option C'}</t>
+          <t>Option C</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'option_1',_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Option 1', 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'option_2',_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Option 2', 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'option_3',_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Option 3', 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'option_4',_'label':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Option 4', 'label': 'Option 4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'location_1',_'label':_'location_1'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Location 1', 'label': 'Location 1'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'location_2',_'label':_'location_2'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Location 2', 'label': 'Location 2'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'location_3',_'label':_'location_3'}</t>
+          <t>location_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Location 3', 'label': 'Location 3'}</t>
+          <t>Location 3</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
